--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/93.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/93.xlsx
@@ -426,13 +426,13 @@
         <v>-10.740987291567</v>
       </c>
       <c r="E2">
-        <v>-11.2364095339859</v>
+        <v>-11.24241429052007</v>
       </c>
       <c r="F2">
-        <v>-3.924334389026775</v>
+        <v>-3.780524009328961</v>
       </c>
       <c r="G2">
-        <v>-10.14215866986969</v>
+        <v>-9.135706478293699</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.3724189831561</v>
       </c>
       <c r="E3">
-        <v>-11.99491987332267</v>
+        <v>-12.00000534963328</v>
       </c>
       <c r="F3">
-        <v>-3.772127677334186</v>
+        <v>-4.106059144750723</v>
       </c>
       <c r="G3">
-        <v>-10.04897674457582</v>
+        <v>-9.056309664625358</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.947828340321662</v>
       </c>
       <c r="E4">
-        <v>-12.10040614685734</v>
+        <v>-12.32558904536276</v>
       </c>
       <c r="F4">
-        <v>-3.789177963586008</v>
+        <v>-3.896338884281763</v>
       </c>
       <c r="G4">
-        <v>-9.305666575734342</v>
+        <v>-9.188787765470373</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.491646064816294</v>
       </c>
       <c r="E5">
-        <v>-13.04956524191703</v>
+        <v>-13.27817166677225</v>
       </c>
       <c r="F5">
-        <v>-3.999562574712012</v>
+        <v>-4.111358211026431</v>
       </c>
       <c r="G5">
-        <v>-9.820651729277829</v>
+        <v>-9.146707421120697</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.001671336609284</v>
       </c>
       <c r="E6">
-        <v>-13.30796902574272</v>
+        <v>-14.12273206920277</v>
       </c>
       <c r="F6">
-        <v>-4.129092728752966</v>
+        <v>-4.156822327561679</v>
       </c>
       <c r="G6">
-        <v>-9.677099853603952</v>
+        <v>-8.990486087668028</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.467530089663411</v>
       </c>
       <c r="E7">
-        <v>-14.77646257695006</v>
+        <v>-14.35539600676886</v>
       </c>
       <c r="F7">
-        <v>-4.113965083243041</v>
+        <v>-4.183441085683238</v>
       </c>
       <c r="G7">
-        <v>-9.522993958750877</v>
+        <v>-8.738815105227093</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.889281161837528</v>
       </c>
       <c r="E8">
-        <v>-15.73121433740923</v>
+        <v>-16.13386813227525</v>
       </c>
       <c r="F8">
-        <v>-4.049095631929812</v>
+        <v>-4.083245906477624</v>
       </c>
       <c r="G8">
-        <v>-8.437982521527982</v>
+        <v>-8.496771189214359</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.251566622889586</v>
       </c>
       <c r="E9">
-        <v>-16.96307700781976</v>
+        <v>-16.79005307293469</v>
       </c>
       <c r="F9">
-        <v>-4.208821434537612</v>
+        <v>-3.793994920033287</v>
       </c>
       <c r="G9">
-        <v>-9.331462346576343</v>
+        <v>-8.108718972737609</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.560125359933046</v>
       </c>
       <c r="E10">
-        <v>-17.40270579295841</v>
+        <v>-16.96555408310196</v>
       </c>
       <c r="F10">
-        <v>-4.378451197813284</v>
+        <v>-4.167293719900467</v>
       </c>
       <c r="G10">
-        <v>-8.641038142724719</v>
+        <v>-8.076954288288302</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.810708859262334</v>
       </c>
       <c r="E11">
-        <v>-18.71001736881074</v>
+        <v>-18.63341370249699</v>
       </c>
       <c r="F11">
-        <v>-4.251976062753855</v>
+        <v>-4.301947326327736</v>
       </c>
       <c r="G11">
-        <v>-7.154123166488762</v>
+        <v>-7.040213915573519</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.031070995865794</v>
       </c>
       <c r="E12">
-        <v>-19.38077493882687</v>
+        <v>-19.19508033366834</v>
       </c>
       <c r="F12">
-        <v>-4.135102534260276</v>
+        <v>-4.320077803672808</v>
       </c>
       <c r="G12">
-        <v>-7.017993533913931</v>
+        <v>-6.380263283410886</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.240849334216962</v>
       </c>
       <c r="E13">
-        <v>-21.05603861322445</v>
+        <v>-19.97287744380378</v>
       </c>
       <c r="F13">
-        <v>-4.165482080390545</v>
+        <v>-3.971579495478042</v>
       </c>
       <c r="G13">
-        <v>-6.828961383621546</v>
+        <v>-6.061845081807165</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.493657564302426</v>
       </c>
       <c r="E14">
-        <v>-21.38029999454368</v>
+        <v>-20.74620495009365</v>
       </c>
       <c r="F14">
-        <v>-4.053186110164836</v>
+        <v>-3.814330511404612</v>
       </c>
       <c r="G14">
-        <v>-6.011451957608379</v>
+        <v>-4.918918960920259</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.828163253747496</v>
       </c>
       <c r="E15">
-        <v>-22.43937873919156</v>
+        <v>-22.12762500308151</v>
       </c>
       <c r="F15">
-        <v>-3.992332584020378</v>
+        <v>-3.582197942485509</v>
       </c>
       <c r="G15">
-        <v>-4.925089817805461</v>
+        <v>-4.75975124193764</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.306321345518436</v>
       </c>
       <c r="E16">
-        <v>-23.31048052778103</v>
+        <v>-22.23106440636471</v>
       </c>
       <c r="F16">
-        <v>-4.085486640302197</v>
+        <v>-3.491433726160768</v>
       </c>
       <c r="G16">
-        <v>-5.262037142792482</v>
+        <v>-4.300734171281072</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.960760629074671</v>
       </c>
       <c r="E17">
-        <v>-24.85437317121609</v>
+        <v>-22.88635723764465</v>
       </c>
       <c r="F17">
-        <v>-3.682242358823814</v>
+        <v>-3.651272186735349</v>
       </c>
       <c r="G17">
-        <v>-3.590943276024712</v>
+        <v>-4.122100444527538</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.830633655140586</v>
       </c>
       <c r="E18">
-        <v>-24.9536237360422</v>
+        <v>-24.8805930357205</v>
       </c>
       <c r="F18">
-        <v>-3.312613226551036</v>
+        <v>-3.205448164018266</v>
       </c>
       <c r="G18">
-        <v>-4.505554313250241</v>
+        <v>-3.938782295835936</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.915254987391832</v>
       </c>
       <c r="E19">
-        <v>-26.5283009457814</v>
+        <v>-24.96803334033461</v>
       </c>
       <c r="F19">
-        <v>-2.833315705454228</v>
+        <v>-2.695210292059494</v>
       </c>
       <c r="G19">
-        <v>-4.195554828952887</v>
+        <v>-3.543479984628181</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.213651282541132</v>
       </c>
       <c r="E20">
-        <v>-26.76524881975874</v>
+        <v>-26.09196888972034</v>
       </c>
       <c r="F20">
-        <v>-2.801141915529495</v>
+        <v>-2.42682091028726</v>
       </c>
       <c r="G20">
-        <v>-4.004850853163171</v>
+        <v>-3.57423495268801</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.688904268212</v>
       </c>
       <c r="E21">
-        <v>-28.09569184084226</v>
+        <v>-26.80890783766669</v>
       </c>
       <c r="F21">
-        <v>-2.630320131561195</v>
+        <v>-2.490691350512713</v>
       </c>
       <c r="G21">
-        <v>-4.362734068140543</v>
+        <v>-3.360992782866935</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.30554686539671</v>
       </c>
       <c r="E22">
-        <v>-28.44846902298779</v>
+        <v>-27.36082466429953</v>
       </c>
       <c r="F22">
-        <v>-1.919077252578317</v>
+        <v>-1.934149397472254</v>
       </c>
       <c r="G22">
-        <v>-4.634950296198195</v>
+        <v>-3.447997230184521</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.0021820291788</v>
       </c>
       <c r="E23">
-        <v>-29.08932055065727</v>
+        <v>-27.78912320747099</v>
       </c>
       <c r="F23">
-        <v>-1.853166543439769</v>
+        <v>-1.586023026241345</v>
       </c>
       <c r="G23">
-        <v>-5.47054192194686</v>
+        <v>-4.100002553052903</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.724869505904131</v>
       </c>
       <c r="E24">
-        <v>-29.36987762932848</v>
+        <v>-27.85226824903394</v>
       </c>
       <c r="F24">
-        <v>-1.581997989031142</v>
+        <v>-1.717638181035144</v>
       </c>
       <c r="G24">
-        <v>-5.856478699824017</v>
+        <v>-4.023290591816911</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.407575173420943</v>
       </c>
       <c r="E25">
-        <v>-28.8705997845608</v>
+        <v>-28.41747161840529</v>
       </c>
       <c r="F25">
-        <v>-1.606287378016029</v>
+        <v>-1.338851447124417</v>
       </c>
       <c r="G25">
-        <v>-5.558724923476427</v>
+        <v>-4.223757366401939</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.998957648425725</v>
       </c>
       <c r="E26">
-        <v>-29.53650283044071</v>
+        <v>-28.70574068831156</v>
       </c>
       <c r="F26">
-        <v>-1.478648386755667</v>
+        <v>-1.360615143898168</v>
       </c>
       <c r="G26">
-        <v>-6.21971837748393</v>
+        <v>-4.538778948282367</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.450634255272059</v>
       </c>
       <c r="E27">
-        <v>-29.76133250797353</v>
+        <v>-28.06457216746155</v>
       </c>
       <c r="F27">
-        <v>-1.541639100799347</v>
+        <v>-1.438489135067947</v>
       </c>
       <c r="G27">
-        <v>-6.914459532718763</v>
+        <v>-5.544095622738388</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.734252088256174</v>
       </c>
       <c r="E28">
-        <v>-29.27380152478175</v>
+        <v>-28.01466838389702</v>
       </c>
       <c r="F28">
-        <v>-1.154450236322025</v>
+        <v>-1.200418000238175</v>
       </c>
       <c r="G28">
-        <v>-6.616056889445477</v>
+        <v>-6.014560559869755</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.830157319493236</v>
       </c>
       <c r="E29">
-        <v>-29.50427368092812</v>
+        <v>-29.04496414775214</v>
       </c>
       <c r="F29">
-        <v>-1.343702366635211</v>
+        <v>-1.313469441535237</v>
       </c>
       <c r="G29">
-        <v>-6.867754356250726</v>
+        <v>-5.810273415732409</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.735282673600477</v>
       </c>
       <c r="E30">
-        <v>-29.06610759289395</v>
+        <v>-28.3917951707818</v>
       </c>
       <c r="F30">
-        <v>-1.484227441213522</v>
+        <v>-1.500993597446184</v>
       </c>
       <c r="G30">
-        <v>-7.134994834362853</v>
+        <v>-5.826279903414785</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.455185635674342</v>
       </c>
       <c r="E31">
-        <v>-28.81071524428337</v>
+        <v>-28.50021589547344</v>
       </c>
       <c r="F31">
-        <v>-1.271902793630161</v>
+        <v>-1.288503276382263</v>
       </c>
       <c r="G31">
-        <v>-7.206035831090073</v>
+        <v>-6.184749084952609</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.010309726691959</v>
       </c>
       <c r="E32">
-        <v>-28.65527990244409</v>
+        <v>-28.21891614706497</v>
       </c>
       <c r="F32">
-        <v>-1.830749264785208</v>
+        <v>-1.417640784274289</v>
       </c>
       <c r="G32">
-        <v>-7.072753267679015</v>
+        <v>-5.936941509156003</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.429586568599422</v>
       </c>
       <c r="E33">
-        <v>-28.4434560022613</v>
+        <v>-27.20584669833503</v>
       </c>
       <c r="F33">
-        <v>-1.707693630364536</v>
+        <v>-1.655657246855477</v>
       </c>
       <c r="G33">
-        <v>-7.381455018124975</v>
+        <v>-5.779839570589889</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.754520321344448</v>
       </c>
       <c r="E34">
-        <v>-27.49801478436191</v>
+        <v>-27.72279917715465</v>
       </c>
       <c r="F34">
-        <v>-1.396366652635592</v>
+        <v>-1.620522043465736</v>
       </c>
       <c r="G34">
-        <v>-6.794207276550277</v>
+        <v>-5.204433650409164</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.028750257524168</v>
       </c>
       <c r="E35">
-        <v>-27.88477816393501</v>
+        <v>-27.38190471080524</v>
       </c>
       <c r="F35">
-        <v>-1.255733890294918</v>
+        <v>-1.767123192943581</v>
       </c>
       <c r="G35">
-        <v>-7.119753082700049</v>
+        <v>-4.896225171248555</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.300808718026745</v>
       </c>
       <c r="E36">
-        <v>-26.78718927632591</v>
+        <v>-26.38482530379638</v>
       </c>
       <c r="F36">
-        <v>-1.493322086928858</v>
+        <v>-1.75570414829599</v>
       </c>
       <c r="G36">
-        <v>-6.7491341990331</v>
+        <v>-5.392578574497024</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.612917139206309</v>
       </c>
       <c r="E37">
-        <v>-26.65796474204302</v>
+        <v>-26.23633211261086</v>
       </c>
       <c r="F37">
-        <v>-1.806666967651021</v>
+        <v>-1.57112318176719</v>
       </c>
       <c r="G37">
-        <v>-5.825736973946345</v>
+        <v>-4.848050112561081</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.006569877663353</v>
       </c>
       <c r="E38">
-        <v>-26.60980894944546</v>
+        <v>-25.51655381146169</v>
       </c>
       <c r="F38">
-        <v>-2.011476666156185</v>
+        <v>-1.774731747538295</v>
       </c>
       <c r="G38">
-        <v>-5.630808742048518</v>
+        <v>-5.252671609461884</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.51092217825817</v>
       </c>
       <c r="E39">
-        <v>-26.99454810113713</v>
+        <v>-24.87692497177429</v>
       </c>
       <c r="F39">
-        <v>-2.026900038828909</v>
+        <v>-2.036495846822938</v>
       </c>
       <c r="G39">
-        <v>-6.013133714742329</v>
+        <v>-4.311185563548551</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.149081557961112</v>
       </c>
       <c r="E40">
-        <v>-26.44255429044616</v>
+        <v>-25.17780584179192</v>
       </c>
       <c r="F40">
-        <v>-2.072115645143317</v>
+        <v>-2.119476723030976</v>
       </c>
       <c r="G40">
-        <v>-5.763055104705784</v>
+        <v>-4.077874866668415</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.9285027064108416</v>
       </c>
       <c r="E41">
-        <v>-25.11735071378952</v>
+        <v>-24.66347082094874</v>
       </c>
       <c r="F41">
-        <v>-2.148861399910483</v>
+        <v>-1.999499301879107</v>
       </c>
       <c r="G41">
-        <v>-5.847119787584497</v>
+        <v>-4.13654104416984</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.8497827797007536</v>
       </c>
       <c r="E42">
-        <v>-25.33050598533057</v>
+        <v>-23.40200551595006</v>
       </c>
       <c r="F42">
-        <v>-1.964464330945104</v>
+        <v>-2.505303751498096</v>
       </c>
       <c r="G42">
-        <v>-5.074613917632184</v>
+        <v>-5.094977083244241</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8983134161728447</v>
       </c>
       <c r="E43">
-        <v>-24.20237254053973</v>
+        <v>-23.43332444218711</v>
       </c>
       <c r="F43">
-        <v>-2.300408731150444</v>
+        <v>-2.28237268768929</v>
       </c>
       <c r="G43">
-        <v>-6.290289276744573</v>
+        <v>-4.034582862651365</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.054186830902826</v>
       </c>
       <c r="E44">
-        <v>-23.29394706917903</v>
+        <v>-22.95767617479145</v>
       </c>
       <c r="F44">
-        <v>-2.460788115639053</v>
+        <v>-2.153147372852568</v>
       </c>
       <c r="G44">
-        <v>-5.379131138516504</v>
+        <v>-4.445656612808207</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.288912153289523</v>
       </c>
       <c r="E45">
-        <v>-23.46425844813351</v>
+        <v>-22.04675098577852</v>
       </c>
       <c r="F45">
-        <v>-2.547215000242737</v>
+        <v>-2.450870072725335</v>
       </c>
       <c r="G45">
-        <v>-5.767782563735863</v>
+        <v>-4.118150963699188</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.573701324512575</v>
       </c>
       <c r="E46">
-        <v>-22.63307062944763</v>
+        <v>-22.08507093283143</v>
       </c>
       <c r="F46">
-        <v>-2.574725910057111</v>
+        <v>-2.327222983979064</v>
       </c>
       <c r="G46">
-        <v>-5.118276702749631</v>
+        <v>-4.374546094624662</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.876915760351885</v>
       </c>
       <c r="E47">
-        <v>-21.3396342979548</v>
+        <v>-22.13803596482514</v>
       </c>
       <c r="F47">
-        <v>-2.646477437752799</v>
+        <v>-2.518721646688642</v>
       </c>
       <c r="G47">
-        <v>-5.709252118601548</v>
+        <v>-4.456372848718829</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.170776120870205</v>
       </c>
       <c r="E48">
-        <v>-22.30825677429946</v>
+        <v>-20.88835827766843</v>
       </c>
       <c r="F48">
-        <v>-3.001246487186757</v>
+        <v>-2.437241772214477</v>
       </c>
       <c r="G48">
-        <v>-5.7049318566728</v>
+        <v>-4.309225720589303</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.430526618757499</v>
       </c>
       <c r="E49">
-        <v>-21.40052868793595</v>
+        <v>-19.92660549639341</v>
       </c>
       <c r="F49">
-        <v>-2.807896423331922</v>
+        <v>-2.681639977266832</v>
       </c>
       <c r="G49">
-        <v>-5.177446083173025</v>
+        <v>-4.116237468377489</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.637728388143967</v>
       </c>
       <c r="E50">
-        <v>-20.85366110982166</v>
+        <v>-20.55505806222988</v>
       </c>
       <c r="F50">
-        <v>-2.769903352402523</v>
+        <v>-2.51081156635931</v>
       </c>
       <c r="G50">
-        <v>-4.619943593268679</v>
+        <v>-3.970599949013871</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.77896762688847</v>
       </c>
       <c r="E51">
-        <v>-20.98940211820158</v>
+        <v>-19.8905860141364</v>
       </c>
       <c r="F51">
-        <v>-2.912015578924597</v>
+        <v>-2.916888035987864</v>
       </c>
       <c r="G51">
-        <v>-6.22285346410962</v>
+        <v>-4.737921504651686</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.847702841578407</v>
       </c>
       <c r="E52">
-        <v>-20.06943809506934</v>
+        <v>-18.66269028695658</v>
       </c>
       <c r="F52">
-        <v>-2.885911236960176</v>
+        <v>-2.728683790439219</v>
       </c>
       <c r="G52">
-        <v>-5.562217549020358</v>
+        <v>-4.091484519380359</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.84345419735544</v>
       </c>
       <c r="E53">
-        <v>-19.43161158803698</v>
+        <v>-18.44746097432002</v>
       </c>
       <c r="F53">
-        <v>-3.169540093841713</v>
+        <v>-2.756974193979628</v>
       </c>
       <c r="G53">
-        <v>-5.706527539622728</v>
+        <v>-4.266003238028579</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.772043008710123</v>
       </c>
       <c r="E54">
-        <v>-19.18630415104148</v>
+        <v>-18.05582042824066</v>
       </c>
       <c r="F54">
-        <v>-3.273044600821512</v>
+        <v>-3.047548911533639</v>
       </c>
       <c r="G54">
-        <v>-5.780346084057397</v>
+        <v>-4.545833720826554</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.6452082946323</v>
       </c>
       <c r="E55">
-        <v>-17.68040540453078</v>
+        <v>-17.03490766252943</v>
       </c>
       <c r="F55">
-        <v>-3.366558168556145</v>
+        <v>-2.847875919293235</v>
       </c>
       <c r="G55">
-        <v>-5.536024512713644</v>
+        <v>-3.646255870894855</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.478828095045645</v>
       </c>
       <c r="E56">
-        <v>-17.74333760781537</v>
+        <v>-17.32451263226796</v>
       </c>
       <c r="F56">
-        <v>-2.91734529479421</v>
+        <v>-3.004057966151859</v>
       </c>
       <c r="G56">
-        <v>-5.612458388124337</v>
+        <v>-4.499731063646664</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.292101303207235</v>
       </c>
       <c r="E57">
-        <v>-17.67607165490544</v>
+        <v>-15.97605534158194</v>
       </c>
       <c r="F57">
-        <v>-3.454846394713919</v>
+        <v>-2.655362506515226</v>
       </c>
       <c r="G57">
-        <v>-5.83588710656975</v>
+        <v>-4.623621609362809</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.104385404903593</v>
       </c>
       <c r="E58">
-        <v>-17.17573867569397</v>
+        <v>-16.24643693915791</v>
       </c>
       <c r="F58">
-        <v>-3.252678359856283</v>
+        <v>-3.289680703371934</v>
       </c>
       <c r="G58">
-        <v>-5.520796003232997</v>
+        <v>-4.811551347990616</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.934675214954642</v>
       </c>
       <c r="E59">
-        <v>-16.77274524527738</v>
+        <v>-15.93555267005734</v>
       </c>
       <c r="F59">
-        <v>-3.214868358122902</v>
+        <v>-2.998381164340474</v>
       </c>
       <c r="G59">
-        <v>-5.937812182632832</v>
+        <v>-4.883204795642602</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.79833047298683</v>
       </c>
       <c r="E60">
-        <v>-16.22331455087475</v>
+        <v>-15.40435361200959</v>
       </c>
       <c r="F60">
-        <v>-3.446514675376561</v>
+        <v>-3.342267951203855</v>
       </c>
       <c r="G60">
-        <v>-5.871058342378968</v>
+        <v>-5.070763753170011</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.708652120645543</v>
       </c>
       <c r="E61">
-        <v>-15.95002567298585</v>
+        <v>-14.9975245641085</v>
       </c>
       <c r="F61">
-        <v>-3.33006941283023</v>
+        <v>-3.399870963659727</v>
       </c>
       <c r="G61">
-        <v>-5.988175511921764</v>
+        <v>-5.431172914393848</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.673010556270841</v>
       </c>
       <c r="E62">
-        <v>-16.30828230868067</v>
+        <v>-14.60743728461377</v>
       </c>
       <c r="F62">
-        <v>-3.501720392568732</v>
+        <v>-3.068189342109194</v>
       </c>
       <c r="G62">
-        <v>-6.400838323937457</v>
+        <v>-5.187189018695101</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.696069427352628</v>
       </c>
       <c r="E63">
-        <v>-15.25292144119309</v>
+        <v>-14.62024833758147</v>
       </c>
       <c r="F63">
-        <v>-3.383540528680938</v>
+        <v>-3.185669235541623</v>
       </c>
       <c r="G63">
-        <v>-6.421734487381336</v>
+        <v>-5.519855808299844</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.775587979846321</v>
       </c>
       <c r="E64">
-        <v>-15.36827073111647</v>
+        <v>-13.80354257877213</v>
       </c>
       <c r="F64">
-        <v>-3.438222717674539</v>
+        <v>-3.044322420499734</v>
       </c>
       <c r="G64">
-        <v>-6.517405942920734</v>
+        <v>-5.40490373553973</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.907066327773035</v>
       </c>
       <c r="E65">
-        <v>-15.19891033170361</v>
+        <v>-13.69086508851327</v>
       </c>
       <c r="F65">
-        <v>-3.517143765241456</v>
+        <v>-3.439110727530339</v>
       </c>
       <c r="G65">
-        <v>-6.942347568341584</v>
+        <v>-5.958774556987496</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.079172242117444</v>
       </c>
       <c r="E66">
-        <v>-14.98626224925142</v>
+        <v>-13.1216313772751</v>
       </c>
       <c r="F66">
-        <v>-3.744933203867681</v>
+        <v>-3.572565686325757</v>
       </c>
       <c r="G66">
-        <v>-6.913413400328354</v>
+        <v>-5.873008253701598</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.280353546493109</v>
       </c>
       <c r="E67">
-        <v>-14.01455135363353</v>
+        <v>-13.94476304070132</v>
       </c>
       <c r="F67">
-        <v>-3.489152402333458</v>
+        <v>-3.628655271536714</v>
       </c>
       <c r="G67">
-        <v>-6.743678419984381</v>
+        <v>-5.821456438564067</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.494127450577057</v>
       </c>
       <c r="E68">
-        <v>-14.85276736397931</v>
+        <v>-13.27478889668852</v>
       </c>
       <c r="F68">
-        <v>-3.904065067047674</v>
+        <v>-3.720227146079186</v>
       </c>
       <c r="G68">
-        <v>-6.524248840550408</v>
+        <v>-5.647126421011586</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.707565938917826</v>
       </c>
       <c r="E69">
-        <v>-14.3345786117556</v>
+        <v>-13.79992432804</v>
       </c>
       <c r="F69">
-        <v>-3.591628076998979</v>
+        <v>-3.523928922637787</v>
       </c>
       <c r="G69">
-        <v>-6.823207655474293</v>
+        <v>-5.855617957983807</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.906091370327538</v>
       </c>
       <c r="E70">
-        <v>-14.84532708118471</v>
+        <v>-13.53824192903276</v>
       </c>
       <c r="F70">
-        <v>-3.518605833707397</v>
+        <v>-3.806455222506197</v>
       </c>
       <c r="G70">
-        <v>-6.50857009687642</v>
+        <v>-6.19337305608241</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.081862811833539</v>
       </c>
       <c r="E71">
-        <v>-14.41919314858892</v>
+        <v>-14.31991994139277</v>
       </c>
       <c r="F71">
-        <v>-3.882520887635664</v>
+        <v>-3.924030378189948</v>
       </c>
       <c r="G71">
-        <v>-6.748640927747748</v>
+        <v>-5.765759820411368</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.227287495385499</v>
       </c>
       <c r="E72">
-        <v>-14.37378161124</v>
+        <v>-13.36922569364448</v>
       </c>
       <c r="F72">
-        <v>-3.919144667248236</v>
+        <v>-3.728219234781395</v>
       </c>
       <c r="G72">
-        <v>-6.073885535933495</v>
+        <v>-5.003781485273938</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.342952339547244</v>
       </c>
       <c r="E73">
-        <v>-14.8592566672323</v>
+        <v>-13.45562444923682</v>
       </c>
       <c r="F73">
-        <v>-3.931759046058067</v>
+        <v>-3.847765904883809</v>
       </c>
       <c r="G73">
-        <v>-6.501952316343417</v>
+        <v>-6.021002881489177</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.429494125266205</v>
       </c>
       <c r="E74">
-        <v>-13.80012358089633</v>
+        <v>-13.62615319494366</v>
       </c>
       <c r="F74">
-        <v>-4.045102072680915</v>
+        <v>-3.778672608183705</v>
       </c>
       <c r="G74">
-        <v>-6.044623623911877</v>
+        <v>-5.569937741217939</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.495462820958436</v>
       </c>
       <c r="E75">
-        <v>-14.3290312310962</v>
+        <v>-14.18248981220799</v>
       </c>
       <c r="F75">
-        <v>-4.058830605647511</v>
+        <v>-4.110048562162604</v>
       </c>
       <c r="G75">
-        <v>-6.4464311571043</v>
+        <v>-5.631666173343189</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.546381049626163</v>
       </c>
       <c r="E76">
-        <v>-15.30841336168309</v>
+        <v>-14.54801464868512</v>
       </c>
       <c r="F76">
-        <v>-4.373783347498509</v>
+        <v>-4.233698964378487</v>
       </c>
       <c r="G76">
-        <v>-6.028332429313124</v>
+        <v>-5.376495944267244</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.594017331852522</v>
       </c>
       <c r="E77">
-        <v>-15.22550605955066</v>
+        <v>-14.11627446526783</v>
       </c>
       <c r="F77">
-        <v>-4.061433336027108</v>
+        <v>-4.286018649539304</v>
       </c>
       <c r="G77">
-        <v>-5.207012565384256</v>
+        <v>-5.469386541553654</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.643385736895907</v>
       </c>
       <c r="E78">
-        <v>-15.84235667497948</v>
+        <v>-14.66391188396342</v>
       </c>
       <c r="F78">
-        <v>-4.271057505877342</v>
+        <v>-4.283888088579303</v>
       </c>
       <c r="G78">
-        <v>-5.531204358408465</v>
+        <v>-5.088581109262369</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.704768396643864</v>
       </c>
       <c r="E79">
-        <v>-16.06389415190872</v>
+        <v>-15.33213350853526</v>
       </c>
       <c r="F79">
-        <v>-4.608963480092511</v>
+        <v>-4.324346380899434</v>
       </c>
       <c r="G79">
-        <v>-5.190304242047555</v>
+        <v>-5.047444270391384</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.778811839527025</v>
       </c>
       <c r="E80">
-        <v>-16.9994089547833</v>
+        <v>-15.19541887824369</v>
       </c>
       <c r="F80">
-        <v>-4.37069767892308</v>
+        <v>-4.18133786084753</v>
       </c>
       <c r="G80">
-        <v>-5.574304350784237</v>
+        <v>-4.184136757387941</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.871378906770729</v>
       </c>
       <c r="E81">
-        <v>-16.30688753868631</v>
+        <v>-16.60652307835183</v>
       </c>
       <c r="F81">
-        <v>-4.503766618508793</v>
+        <v>-4.526747186997257</v>
       </c>
       <c r="G81">
-        <v>-5.13354493877675</v>
+        <v>-4.079943957630459</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.977085270757455</v>
       </c>
       <c r="E82">
-        <v>-16.7747060745227</v>
+        <v>-17.41103365665851</v>
       </c>
       <c r="F82">
-        <v>-4.813207403661562</v>
+        <v>-4.978059143757886</v>
       </c>
       <c r="G82">
-        <v>-5.031298739796359</v>
+        <v>-4.337736138773506</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.097487467505957</v>
       </c>
       <c r="E83">
-        <v>-17.91246252657984</v>
+        <v>-17.25618701644024</v>
       </c>
       <c r="F83">
-        <v>-5.145781176904911</v>
+        <v>-4.633056546002934</v>
       </c>
       <c r="G83">
-        <v>-4.73267760051748</v>
+        <v>-4.342688714900256</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.223759166173798</v>
       </c>
       <c r="E84">
-        <v>-19.37023717981103</v>
+        <v>-18.12131121933959</v>
       </c>
       <c r="F84">
-        <v>-5.010455764513972</v>
+        <v>-5.144329877215206</v>
       </c>
       <c r="G84">
-        <v>-4.689385596500431</v>
+        <v>-4.047119898608585</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.356632162428171</v>
       </c>
       <c r="E85">
-        <v>-19.79548805997532</v>
+        <v>-19.03765246326569</v>
       </c>
       <c r="F85">
-        <v>-4.973260411393468</v>
+        <v>-4.889192717152958</v>
       </c>
       <c r="G85">
-        <v>-4.507851831854495</v>
+        <v>-4.665754922441113</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.48587751450166</v>
       </c>
       <c r="E86">
-        <v>-21.02403588741224</v>
+        <v>-21.74803472633656</v>
       </c>
       <c r="F86">
-        <v>-5.124983356522823</v>
+        <v>-5.068682537624152</v>
       </c>
       <c r="G86">
-        <v>-4.912450154936524</v>
+        <v>-3.85477389223139</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.611815851581672</v>
       </c>
       <c r="E87">
-        <v>-23.07227373802956</v>
+        <v>-21.70985969045189</v>
       </c>
       <c r="F87">
-        <v>-5.689109013135912</v>
+        <v>-5.1737700547107</v>
       </c>
       <c r="G87">
-        <v>-5.079589667577708</v>
+        <v>-3.441217232920094</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.723323327660458</v>
       </c>
       <c r="E88">
-        <v>-24.17689534577258</v>
+        <v>-23.55213801472636</v>
       </c>
       <c r="F88">
-        <v>-5.212008322391329</v>
+        <v>-5.36918689523552</v>
       </c>
       <c r="G88">
-        <v>-4.541371105439616</v>
+        <v>-4.357986745837228</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.822233323250777</v>
       </c>
       <c r="E89">
-        <v>-25.08526647544518</v>
+        <v>-24.4911125717428</v>
       </c>
       <c r="F89">
-        <v>-5.889643507475228</v>
+        <v>-5.444570813992484</v>
       </c>
       <c r="G89">
-        <v>-5.060133591443411</v>
+        <v>-4.221337357612732</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.899849651706545</v>
       </c>
       <c r="E90">
-        <v>-26.53106784340009</v>
+        <v>-26.79311252032794</v>
       </c>
       <c r="F90">
-        <v>-5.724954127389852</v>
+        <v>-5.417652186871111</v>
       </c>
       <c r="G90">
-        <v>-5.3971371957046</v>
+        <v>-4.336623795472311</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.963615605876493</v>
       </c>
       <c r="E91">
-        <v>-28.16576544763695</v>
+        <v>-28.71196734007211</v>
       </c>
       <c r="F91">
-        <v>-5.713656852750472</v>
+        <v>-5.626022208473508</v>
       </c>
       <c r="G91">
-        <v>-5.932929127962407</v>
+        <v>-4.676378463076635</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.009349727578444</v>
       </c>
       <c r="E92">
-        <v>-29.89707351635345</v>
+        <v>-30.52050400451542</v>
       </c>
       <c r="F92">
-        <v>-5.795805219718697</v>
+        <v>-5.75953515298712</v>
       </c>
       <c r="G92">
-        <v>-6.106213013124478</v>
+        <v>-5.34908131665654</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.050288113083255</v>
       </c>
       <c r="E93">
-        <v>-31.29582630360566</v>
+        <v>-31.54368327146749</v>
       </c>
       <c r="F93">
-        <v>-5.741895069144505</v>
+        <v>-5.807487685200378</v>
       </c>
       <c r="G93">
-        <v>-6.443425181754641</v>
+        <v>-5.563770194878276</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.086109661120073</v>
       </c>
       <c r="E94">
-        <v>-34.19536971868793</v>
+        <v>-34.11604443949557</v>
       </c>
       <c r="F94">
-        <v>-5.951896146163013</v>
+        <v>-5.833999583926976</v>
       </c>
       <c r="G94">
-        <v>-6.400047103553571</v>
+        <v>-5.699913069635264</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.132504225309381</v>
       </c>
       <c r="E95">
-        <v>-36.9815609008842</v>
+        <v>-35.65957933348402</v>
       </c>
       <c r="F95">
-        <v>-5.909638639844002</v>
+        <v>-5.743673573958316</v>
       </c>
       <c r="G95">
-        <v>-7.301048488067156</v>
+        <v>-6.330456125772551</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.193859103234047</v>
       </c>
       <c r="E96">
-        <v>-38.3890445860232</v>
+        <v>-38.1652315509051</v>
       </c>
       <c r="F96">
-        <v>-6.019619323178887</v>
+        <v>-5.621903565746788</v>
       </c>
       <c r="G96">
-        <v>-7.355017001448355</v>
+        <v>-6.445490962171147</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.282558371302136</v>
       </c>
       <c r="E97">
-        <v>-41.85589937512738</v>
+        <v>-40.56320571337181</v>
       </c>
       <c r="F97">
-        <v>-6.467177947237432</v>
+        <v>-5.654806318985984</v>
       </c>
       <c r="G97">
-        <v>-7.134574395079365</v>
+        <v>-7.087730175698678</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.408670204412822</v>
       </c>
       <c r="E98">
-        <v>-42.21024793775358</v>
+        <v>-42.8429799115273</v>
       </c>
       <c r="F98">
-        <v>-5.961231018425161</v>
+        <v>-5.551793862243449</v>
       </c>
       <c r="G98">
-        <v>-7.883337032424026</v>
+        <v>-7.425634248346549</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.573641731483149</v>
       </c>
       <c r="E99">
-        <v>-46.10771305601013</v>
+        <v>-45.30118504253303</v>
       </c>
       <c r="F99">
-        <v>-6.073447465380202</v>
+        <v>-5.700722724123161</v>
       </c>
       <c r="G99">
-        <v>-8.413832091818998</v>
+        <v>-7.746373142373298</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.798307757844042</v>
       </c>
       <c r="E100">
-        <v>-48.62771600756152</v>
+        <v>-47.98278432481113</v>
       </c>
       <c r="F100">
-        <v>-5.980548546258445</v>
+        <v>-5.736614226951658</v>
       </c>
       <c r="G100">
-        <v>-8.909020183037644</v>
+        <v>-7.944294107438626</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.056989761279796</v>
       </c>
       <c r="E101">
-        <v>-49.74992054775782</v>
+        <v>-50.24316306879178</v>
       </c>
       <c r="F101">
-        <v>-6.087547106943251</v>
+        <v>-5.546979390898378</v>
       </c>
       <c r="G101">
-        <v>-9.346528639325566</v>
+        <v>-8.67419656684606</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.405291176464727</v>
       </c>
       <c r="E102">
-        <v>-53.06069808383214</v>
+        <v>-52.6894424634983</v>
       </c>
       <c r="F102">
-        <v>-5.988290468005009</v>
+        <v>-5.787356700577544</v>
       </c>
       <c r="G102">
-        <v>-9.999116618208859</v>
+        <v>-9.039319944917818</v>
       </c>
     </row>
   </sheetData>
